--- a/artfynd/A 32676-2025 artfynd.xlsx
+++ b/artfynd/A 32676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,218 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126379624</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489989</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6865680</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126379625</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80080</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>489737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6865530</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32676-2025 artfynd.xlsx
+++ b/artfynd/A 32676-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>126379624</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>126379625</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32676-2025 artfynd.xlsx
+++ b/artfynd/A 32676-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>7120339</v>
       </c>
       <c r="B2" t="n">
-        <v>77528</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490031.9515107612</v>
+        <v>490032</v>
       </c>
       <c r="R2" t="n">
-        <v>6865805.82663205</v>
+        <v>6865806</v>
       </c>
       <c r="S2" t="n">
         <v>200</v>
@@ -752,19 +747,9 @@
           <t>2011-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>7122898</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490031.9515107612</v>
+        <v>490032</v>
       </c>
       <c r="R3" t="n">
-        <v>6865805.82663205</v>
+        <v>6865806</v>
       </c>
       <c r="S3" t="n">
         <v>200</v>
@@ -873,19 +853,9 @@
           <t>2011-08-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379624</v>
+        <v>126379625</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489989</v>
+        <v>489737</v>
       </c>
       <c r="R4" t="n">
-        <v>6865680</v>
+        <v>6865530</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1023,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379625</v>
+        <v>126379624</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1062,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489737</v>
+        <v>489989</v>
       </c>
       <c r="R5" t="n">
-        <v>6865530</v>
+        <v>6865680</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 32676-2025 artfynd.xlsx
+++ b/artfynd/A 32676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7120339</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7122898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379625</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>